--- a/python_in_excel_environment_exploration_demo.xlsx
+++ b/python_in_excel_environment_exploration_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977AFBFF-1AE3-4C5F-9AEC-067CBE9FDBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214D9BE8-F892-4AD3-AC99-5C59468CB911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -70,18 +70,28 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -90,7 +100,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -122,20 +132,37 @@
       <code>sales.head()</code>
     </pythonScript>
     <pythonScript>
+      <code>%%who</code>
+    </pythonScript>
+    <pythonScript>
+      <code>%%whos</code>
+    </pythonScript>
+    <pythonScript>
       <code>dir()[:10]</code>
     </pythonScript>
     <pythonScript>
-      <code>pd.DataFrame(
-    [
-        {
-            "name": name,
-            "type": type(value).__name__,
-            "shape": str(getattr(value, "shape", "")),
-        }
-        for name, value in globals().items()
-        if not name.startswith("_")
-    ]
-)</code>
+      <code>[name for name in dir() if not name.startswith("_")]</code>
+    </pythonScript>
+    <pythonScript>
+      <code>pd.DataFrame([
+    {
+        "Variable": name,
+        "Type": type(value).__name__,
+        "Preview": repr(value)[:100]
+    }
+    for name, value in globals().items()
+    if not name.startswith("_")
+    and not callable(value)
+    and type(value).__name__ != "module"
+])</code>
+    </pythonScript>
+    <pythonScript>
+      <code>[
+    name
+    for name, value in globals().items()
+    if type(value).__name__ == "module"
+    and not name.startswith("_")
+]</code>
     </pythonScript>
   </pythonScripts>
 </python>
@@ -300,10 +327,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +459,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <rv s="0">
     <fb t="s">Variables loaded</fb>
     <v>&lt;class 'str'&gt;</v>
@@ -443,11 +472,23 @@
     <fb>45658</fb>
     <v>1</v>
   </rv>
+  <rv s="1">
+    <fb>0</fb>
+    <v>2</v>
+  </rv>
+  <rv s="2">
+    <fb>0</fb>
+    <v>&lt;class 'NoneType'&gt;</v>
+    <v>NoneType</v>
+    <v>None</v>
+    <v>2</v>
+    <v>0</v>
+  </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <s t="_python">
     <k n="Python_type" t="s"/>
     <k n="Python_typeName" t="s"/>
@@ -458,12 +499,19 @@
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="preview" t="r"/>
+    <k n="_Provider" t="spb"/>
+  </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="2">
+  <spbData count="3">
     <spb s="0">
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
@@ -471,6 +519,9 @@
     </spb>
     <spb s="1">
       <v>1</v>
+    </spb>
+    <spb s="1">
+      <v>2</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
@@ -491,13 +542,22 @@
 
 <file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
 <richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="1">
+  <dxfs count="2">
     <x:dxf>
       <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="0" formatCode="General"/>
+    </x:dxf>
   </dxfs>
+  <richProperties>
+    <rPr n="NumberFormat" t="s"/>
+  </richProperties>
   <richStyles>
     <rSty dxfid="0"/>
+    <rSty dxfid="1">
+      <rpv i="0">0;-0;"None"</rpv>
+    </rSty>
   </richStyles>
 </richStyleSheet>
 </file>
@@ -2992,48 +3052,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:G40"/>
+  <dimension ref="A2:G57"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="1.73046875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="1.73046875" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.33203125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="9" t="str" cm="1" vm="1">
         <f t="array" ref="B2">_xlfn._xlws.PY(0,1,Sales[#All],Forecast[#All],TaxRate,RegionList)</f>
         <v>Variables loaded</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="str" cm="1">
         <f t="array" ref="B4">_xlfn._xlws.PY(1,0)</f>
         <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B6" s="9" cm="1">
         <f t="array" ref="B6:B7">_xlfn._xlws.PY(2,0)</f>
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B7" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B8" s="9"/>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="str" cm="1">
         <f t="array" ref="B9:G14">_xlfn._xlws.PY(3,0)</f>
         <v>Date</v>
@@ -3041,7 +3101,7 @@
       <c r="C9" t="str">
         <v>Region</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D9" s="10" t="str">
         <v>Product</v>
       </c>
       <c r="E9" t="str">
@@ -3054,14 +3114,14 @@
         <v>Revenue</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B10" s="9" vm="2">
         <v>45658</v>
       </c>
       <c r="C10" t="str">
         <v>North</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="10" t="str">
         <v>Widget</v>
       </c>
       <c r="E10">
@@ -3074,14 +3134,14 @@
         <v>4881.0599999999995</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B11" s="9" vm="2">
         <v>45658</v>
       </c>
       <c r="C11" t="str">
         <v>North</v>
       </c>
-      <c r="D11" t="str">
+      <c r="D11" s="10" t="str">
         <v>Gadget</v>
       </c>
       <c r="E11">
@@ -3094,14 +3154,14 @@
         <v>6793.26</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B12" s="9" vm="2">
         <v>45658</v>
       </c>
       <c r="C12" t="str">
         <v>South</v>
       </c>
-      <c r="D12" t="str">
+      <c r="D12" s="10" t="str">
         <v>Widget</v>
       </c>
       <c r="E12">
@@ -3114,14 +3174,14 @@
         <v>1995.5400000000002</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B13" s="9" vm="2">
         <v>45658</v>
       </c>
       <c r="C13" t="str">
         <v>South</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D13" s="10" t="str">
         <v>Gadget</v>
       </c>
       <c r="E13">
@@ -3134,14 +3194,14 @@
         <v>13653.640000000001</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B14" s="9" vm="2">
         <v>45658</v>
       </c>
       <c r="C14" t="str">
         <v>East</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D14" s="10" t="str">
         <v>Widget</v>
       </c>
       <c r="E14">
@@ -3154,215 +3214,242 @@
         <v>4302.33</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B15" s="9"/>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="9" t="str" cm="1">
-        <f t="array" ref="B16:B25">_xlfn._xlws.PY(4,0)</f>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" s="9" cm="1" vm="3">
+        <f t="array" ref="B16">_xlfn._xlws.PY(4,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="9" cm="1" vm="3">
+        <f t="array" ref="B18">_xlfn._xlws.PY(5,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B20" s="9" t="str" cm="1">
+        <f t="array" ref="B20:B29">_xlfn._xlws.PY(6,0)</f>
         <v>_</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="9" t="str">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B21" s="9" t="str">
         <v>_1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="9" t="str">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B22" s="9" t="str">
         <v>_InteractiveShell</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="9" t="str">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B23" s="9" t="str">
         <v>__</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="9" t="str">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B24" s="9" t="str">
         <v>___</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="9" t="str">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="9" t="str">
         <v>__builtin__</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="9" t="str">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B26" s="9" t="str">
         <v>__builtins__</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="9" t="str">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B27" s="9" t="str">
         <v>__doc__</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="9" t="str">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B28" s="9" t="str">
         <v>__loader__</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="9" t="str">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B29" s="9" t="str">
         <v>__name__</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="9"/>
-    </row>
-    <row r="28" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9" t="str" cm="1">
-        <f t="array" ref="B28:D40">_xlfn._xlws.PY(5,0)</f>
-        <v>name</v>
-      </c>
-      <c r="C28" t="str">
-        <v>type</v>
-      </c>
-      <c r="D28" t="str">
-        <v>shape</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="9"/>
-      <c r="B29" t="str">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B30" s="9"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B31" s="9" t="str" cm="1">
+        <f t="array" ref="B31:B42">_xlfn._xlws.PY(7,0)</f>
+        <v>excel</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B32" s="9" t="str">
+        <v>forecast</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="9" t="str">
         <v>np</v>
       </c>
-      <c r="C29" t="str">
-        <v>module</v>
-      </c>
-      <c r="D29" t="str">
-        <v>&lt;function shape at 0x7f9a0dd2ef20&gt;</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="9"/>
-      <c r="B30" t="str">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="9" t="str">
         <v>pd</v>
       </c>
-      <c r="C30" t="str">
-        <v>module</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="9"/>
-      <c r="B31" t="str">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9" t="str">
         <v>plt</v>
       </c>
-      <c r="C31" t="str">
-        <v>module</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="9"/>
-      <c r="B32" t="str">
-        <v>sns</v>
-      </c>
-      <c r="C32" t="str">
-        <v>module</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="162" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="9"/>
-      <c r="B33" t="str">
-        <v>sm</v>
-      </c>
-      <c r="C33" t="str">
-        <v>module</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="105.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="9"/>
-      <c r="B34" t="str">
-        <v>excel</v>
-      </c>
-      <c r="C34" t="str">
-        <v>module</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B35" t="str">
-        <v>warnings</v>
-      </c>
-      <c r="C35" t="str">
-        <v>module</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="9"/>
       <c r="B36" t="str">
-        <v>xl</v>
-      </c>
-      <c r="C36" t="str">
-        <v>function</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
+        <v>regions</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="9"/>
       <c r="B37" t="str">
         <v>sales</v>
       </c>
-      <c r="C37" t="str">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="9"/>
+      <c r="B38" t="str">
+        <v>sm</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="9"/>
+      <c r="B39" t="str">
+        <v>sns</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="9"/>
+      <c r="B40" t="str">
+        <v>tax_rate</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="9"/>
+      <c r="B41" t="str">
+        <v>warnings</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B42" t="str">
+        <v>xl</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B44" t="str" cm="1">
+        <f t="array" ref="B44:D48">_xlfn._xlws.PY(8,0)</f>
+        <v>Variable</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D44" s="10" t="str">
+        <v>Preview</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B45" t="str">
+        <v>sales</v>
+      </c>
+      <c r="C45" t="str">
         <v>DataFrame</v>
       </c>
-      <c r="D37" t="str">
-        <v>(96, 6)</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B38" t="str">
+      <c r="D45" s="10" t="str">
+        <v xml:space="preserve">         Date Region Product  Units  Unit Price   Revenue
+0  2025-01-01  North  Widget    207       </v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="B46" t="str">
         <v>forecast</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C46" t="str">
         <v>DataFrame</v>
       </c>
-      <c r="D38" t="str">
-        <v>(12, 4)</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B39" t="str">
+      <c r="D46" s="10" t="str">
+        <v xml:space="preserve">        Month  Forecast Revenue    Low   High
+0  2026-01-01             51336  46202  56470
+1  2026-</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B47" t="str">
         <v>tax_rate</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C47" t="str">
         <v>float</v>
       </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B40" t="str">
+      <c r="D47" s="10" t="str">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B48" t="str">
         <v>regions</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C48" t="str">
         <v>list</v>
       </c>
-      <c r="D40" t="str">
-        <v/>
+      <c r="D48" s="10" t="str">
+        <v>['North', 'South', 'East', 'West']</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="str" cm="1">
+        <f t="array" ref="B51:B57">_xlfn._xlws.PY(9,0)</f>
+        <v>np</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" t="str">
+        <v>pd</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B53" t="str">
+        <v>plt</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B54" t="str">
+        <v>sns</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B55" t="str">
+        <v>sm</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B56" t="str">
+        <v>excel</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B57" t="str">
+        <v>warnings</v>
       </c>
     </row>
   </sheetData>
